--- a/artfynd/A 37835-2025 artfynd.xlsx
+++ b/artfynd/A 37835-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127448230</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127450785</v>
       </c>
       <c r="B3" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127450423</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2025 artfynd.xlsx
+++ b/artfynd/A 37835-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127448230</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127450785</v>
       </c>
       <c r="B3" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127450423</v>
       </c>
       <c r="B4" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2025 artfynd.xlsx
+++ b/artfynd/A 37835-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127448230</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127450785</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127450423</v>
       </c>
       <c r="B4" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2025 artfynd.xlsx
+++ b/artfynd/A 37835-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127448230</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127450785</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127450423</v>
       </c>
       <c r="B4" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2025 artfynd.xlsx
+++ b/artfynd/A 37835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>127448230</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127450785</v>
+        <v>127450423</v>
       </c>
       <c r="B3" t="n">
-        <v>57832</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499189</v>
+        <v>499148</v>
       </c>
       <c r="R3" t="n">
-        <v>6846015</v>
+        <v>6845999</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127450423</v>
+        <v>127447983</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>57132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499148</v>
+        <v>499168</v>
       </c>
       <c r="R4" t="n">
-        <v>6845999</v>
+        <v>6845691</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -942,6 +946,11 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tre uppflygande ungfåglar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -963,6 +972,200 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127450785</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>499189</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6846015</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127447622</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hivikilen, Hivikilen, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>499115</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6845767</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37835-2025 artfynd.xlsx
+++ b/artfynd/A 37835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127448230</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127450423</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127447983</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127450785</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,8 +1191,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127447622</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>